--- a/public/kk-sayongnaeyeokseo.xlsx
+++ b/public/kk-sayongnaeyeokseo.xlsx
@@ -975,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AB43"/>
+  <dimension ref="A1:AB60"/>
   <sheetFormatPr defaultRowHeight="24" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="24" width="4" customWidth="1"/>
@@ -1015,7 +1015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -1041,7 +1041,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1070,9 @@
       <c r="V3" s="8"/>
       <c r="W3" s="8"/>
       <c r="X3" s="9"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="11"/>
@@ -1096,6 +1097,7 @@
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
+      <c r="Z4" s="5"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
@@ -1270,7 +1272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30"/>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
@@ -1295,8 +1297,9 @@
       <c r="V10" s="30"/>
       <c r="W10" s="30"/>
       <c r="X10" s="30"/>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z10" s="15"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30"/>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -1321,8 +1324,9 @@
       <c r="V11" s="30"/>
       <c r="W11" s="30"/>
       <c r="X11" s="30"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z11" s="15"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30"/>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -1347,8 +1351,9 @@
       <c r="V12" s="30"/>
       <c r="W12" s="30"/>
       <c r="X12" s="30"/>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z12" s="15"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -1373,8 +1378,9 @@
       <c r="V13" s="30"/>
       <c r="W13" s="30"/>
       <c r="X13" s="30"/>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z13" s="15"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30"/>
       <c r="B14" s="30"/>
       <c r="C14" s="30"/>
@@ -1399,6 +1405,7 @@
       <c r="V14" s="30"/>
       <c r="W14" s="30"/>
       <c r="X14" s="30"/>
+      <c r="Z14" s="15"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="13:28" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M15" s="30"/>
@@ -1413,6 +1420,7 @@
       <c r="V15" s="30"/>
       <c r="W15" s="30"/>
       <c r="X15" s="30"/>
+      <c r="Z15" s="15"/>
       <c r="AB15" s="31"/>
     </row>
     <row r="16" ht="24" customHeight="1" spans="13:28" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -1428,9 +1436,10 @@
       <c r="V16" s="30"/>
       <c r="W16" s="30"/>
       <c r="X16" s="30"/>
+      <c r="Z16" s="15"/>
       <c r="AB16" s="31"/>
     </row>
-    <row r="17" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M17" s="30"/>
       <c r="N17" s="30"/>
       <c r="O17" s="30"/>
@@ -1443,8 +1452,9 @@
       <c r="V17" s="30"/>
       <c r="W17" s="30"/>
       <c r="X17" s="30"/>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z17" s="15"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M18" s="30"/>
       <c r="N18" s="30"/>
       <c r="O18" s="30"/>
@@ -1457,8 +1467,9 @@
       <c r="V18" s="30"/>
       <c r="W18" s="30"/>
       <c r="X18" s="30"/>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z18" s="15"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M19" s="30"/>
       <c r="N19" s="30"/>
       <c r="O19" s="30"/>
@@ -1471,8 +1482,9 @@
       <c r="V19" s="30"/>
       <c r="W19" s="30"/>
       <c r="X19" s="30"/>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z19" s="15"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M20" s="30"/>
       <c r="N20" s="30"/>
       <c r="O20" s="30"/>
@@ -1485,8 +1497,9 @@
       <c r="V20" s="30"/>
       <c r="W20" s="30"/>
       <c r="X20" s="30"/>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z20" s="15"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M21" s="30"/>
       <c r="N21" s="30"/>
       <c r="O21" s="30"/>
@@ -1499,8 +1512,9 @@
       <c r="V21" s="30"/>
       <c r="W21" s="30"/>
       <c r="X21" s="30"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z21" s="15"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M22" s="30"/>
       <c r="N22" s="30"/>
       <c r="O22" s="30"/>
@@ -1513,8 +1527,9 @@
       <c r="V22" s="30"/>
       <c r="W22" s="30"/>
       <c r="X22" s="30"/>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z22" s="15"/>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M23" s="30"/>
       <c r="N23" s="30"/>
       <c r="O23" s="30"/>
@@ -1527,8 +1542,9 @@
       <c r="V23" s="30"/>
       <c r="W23" s="30"/>
       <c r="X23" s="30"/>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z23" s="15"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M24" s="30"/>
       <c r="N24" s="30"/>
       <c r="O24" s="30"/>
@@ -1541,8 +1557,9 @@
       <c r="V24" s="30"/>
       <c r="W24" s="30"/>
       <c r="X24" s="30"/>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z24" s="15"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M25" s="30"/>
       <c r="N25" s="30"/>
       <c r="O25" s="30"/>
@@ -1555,8 +1572,9 @@
       <c r="V25" s="30"/>
       <c r="W25" s="30"/>
       <c r="X25" s="30"/>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z25" s="15"/>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M26" s="30"/>
       <c r="N26" s="30"/>
       <c r="O26" s="30"/>
@@ -1569,8 +1587,9 @@
       <c r="V26" s="30"/>
       <c r="W26" s="30"/>
       <c r="X26" s="30"/>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z26" s="15"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M27" s="30"/>
       <c r="N27" s="30"/>
       <c r="O27" s="30"/>
@@ -1583,8 +1602,9 @@
       <c r="V27" s="30"/>
       <c r="W27" s="30"/>
       <c r="X27" s="30"/>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z27" s="15"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M28" s="30"/>
       <c r="N28" s="30"/>
       <c r="O28" s="30"/>
@@ -1597,8 +1617,9 @@
       <c r="V28" s="30"/>
       <c r="W28" s="30"/>
       <c r="X28" s="30"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z28" s="15"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M29" s="30"/>
       <c r="N29" s="30"/>
       <c r="O29" s="30"/>
@@ -1611,8 +1632,9 @@
       <c r="V29" s="30"/>
       <c r="W29" s="30"/>
       <c r="X29" s="30"/>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="13:24" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z29" s="15"/>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="13:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="M30" s="30"/>
       <c r="N30" s="30"/>
       <c r="O30" s="30"/>
@@ -1625,13 +1647,14 @@
       <c r="V30" s="30"/>
       <c r="W30" s="30"/>
       <c r="X30" s="30"/>
+      <c r="Z30" s="15"/>
     </row>
     <row r="31" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="Z31" s="11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
+      <c r="Z31" s="11"/>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z32" s="15"/>
+    </row>
     <row r="33" ht="24" customHeight="1" spans="1:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="32"/>
       <c r="B33" s="32"/>
@@ -1659,14 +1682,28 @@
       <c r="X33" s="32"/>
       <c r="Z33" s="33"/>
     </row>
-    <row r="34" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="24" customHeight="1" s="15" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z34" s="15"/>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z35" s="15"/>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z36" s="15"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z37" s="15"/>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z38" s="15"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z39" s="15"/>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="26:26" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z40" s="15"/>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="11"/>
       <c r="C41" s="11"/>
@@ -1691,8 +1728,9 @@
       <c r="V41" s="11"/>
       <c r="W41" s="11"/>
       <c r="X41" s="11"/>
-    </row>
-    <row r="42" ht="24" customHeight="1" spans="1:24" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="Z41" s="5"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:26" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="11"/>
       <c r="C42" s="11"/>
@@ -1717,6 +1755,9 @@
       <c r="V42" s="11"/>
       <c r="W42" s="11"/>
       <c r="X42" s="11"/>
+      <c r="Z42" s="11" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43" s="32"/>
@@ -1745,6 +1786,23 @@
       <c r="X43" s="32"/>
       <c r="Z43" s="34"/>
     </row>
+    <row r="44" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="26:26" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="26:26" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A1:E2"/>
@@ -1782,7 +1840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="17" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83203125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -1923,57 +1981,6 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" sqref="C10:C80">
